--- a/my_sdmx_data.xlsx
+++ b/my_sdmx_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:N158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,14 +436,14 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>DM_POP_U5</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>DM_POP_U18</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>DM_POP_U5</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>DM_POP_ADLCNT</t>
@@ -456,57 +456,42 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>DM_POP_CHILD_PROP</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>DM_POP_ADLCNT_PROP</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>DM_POP_GRT</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>DM_BRTS</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>DM_FRATE_TOT</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>DM_LIFE_EXP</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>DM_DPR_TOT</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>DM_DPR_CHD</t>
-        </is>
-      </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>DM_DPR_OLD</t>
+          <t>DM_BRTS_SURVIVING_1</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>DM_POP_URBN</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>DM_POP_U_GRT</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
           <t>DM_NET_MG_RATE</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>DM_POP_ADLCNT_PROP</t>
         </is>
       </c>
     </row>
@@ -516,74 +501,67 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>360046.821</t>
+          <t>358903.761</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>107355.514</t>
+          <t>32764.727</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32727.9435</t>
+          <t>107240.719</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>57839.9075</t>
+          <t>57768.853</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>57355.14</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>57332.757</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>29.877</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>7101.272</t>
+          <t>16.095</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>0.723</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>65.361</t>
+          <t>7129.271</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>51.65</t>
+          <t>2.583</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>37.991</t>
+          <t>65.2835</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>13.66</t>
+          <t>6804.571</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>59.3959823573379</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>-2.377</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>16.0645516434098</t>
+          <t>-1.582</t>
         </is>
       </c>
     </row>
@@ -593,74 +571,67 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>362275.4235</t>
+          <t>361308.221</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>107823.663</t>
+          <t>33197.811</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33117.8155</t>
+          <t>107788.292</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>57571.1155</t>
+          <t>57527.381</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>57110.789</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>57163.784</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>29.832</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6973.249</t>
+          <t>15.922</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.527</t>
+          <t>0.613</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>65.384</t>
+          <t>6980.451</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>51.789</t>
+          <t>2.5296</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>37.949</t>
+          <t>65.3218</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>13.84</t>
+          <t>6671.751</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>59.7887543033316</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>-1.667</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>15.8915321784172</t>
+          <t>-1.829</t>
         </is>
       </c>
     </row>
@@ -670,74 +641,67 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>364615.6255</t>
+          <t>363668.091</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108357.641</t>
+          <t>33187.717</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>33085.907</t>
+          <t>108351.654</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>57211.0155</t>
+          <t>57160.896</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>56878.8765</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>56918.191</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>29.794</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6943.765</t>
+          <t>15.717</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>0.689</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>66.47</t>
+          <t>6941.42</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>51.992</t>
+          <t>2.5181</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>37.966</t>
+          <t>66.4406</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>14.026</t>
+          <t>6646.508</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>60.1593468440138</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>-1.453</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>15.690774475599</t>
+          <t>-1.443</t>
         </is>
       </c>
     </row>
@@ -747,74 +711,67 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>367236.9075</t>
+          <t>366348.571</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>108875.453</t>
+          <t>33064.351</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>32938.71</t>
+          <t>108899.76</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57023.892</t>
+          <t>56959.667</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>56695.9235</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>56723.687</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>29.725</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6916.519</t>
+          <t>15.548</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>66.937</t>
+          <t>6894.847</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>52.209</t>
+          <t>2.5011</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>37.981</t>
+          <t>66.9331</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>14.228</t>
+          <t>6619.52</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>60.5260440876617</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-0.364</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>15.5278216419464</t>
+          <t>-0.236</t>
         </is>
       </c>
     </row>
@@ -824,74 +781,67 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>369958.3805</t>
+          <t>369150.61</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>109474.391</t>
+          <t>32936.961</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>32795.505</t>
+          <t>109543.093</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>57007.0285</t>
+          <t>56926.976</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>56595.2495</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>56611.781</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>29.672</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6941.175</t>
+          <t>15.42</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.517</t>
+          <t>0.744</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.576</t>
+          <t>6930.41</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>52.407</t>
+          <t>2.5125</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>37.994</t>
+          <t>67.6546</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>14.413</t>
+          <t>6666.518</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>60.8996163003978</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>-0.952</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>15.4090382877541</t>
+          <t>-0.869</t>
         </is>
       </c>
     </row>
@@ -901,74 +851,67 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>372647.2225</t>
+          <t>371935.472</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>110182.2005</t>
+          <t>32903.787</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>32763.8005</t>
+          <t>110299.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>56825.5855</t>
+          <t>56737.471</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>56510.941</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>56513.691</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>29.656</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6975.769</t>
+          <t>15.254</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.531</t>
+          <t>0.759</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>67.807</t>
+          <t>6972.791</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>52.617</t>
+          <t>2.5292</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>38.026</t>
+          <t>67.9141</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>14.591</t>
+          <t>6715.974</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>61.2982515845793</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>-0.805</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>15.2491638388637</t>
+          <t>-0.666</t>
         </is>
       </c>
     </row>
@@ -978,74 +921,67 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>375280.3495</t>
+          <t>374652.846</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>110939.715</t>
+          <t>33014.62</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>32889.4945</t>
+          <t>111096.869</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>56879.2845</t>
+          <t>56796.367</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>56334.2025</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>56332.339</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>29.655</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7027.426</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.549</t>
+          <t>0.697</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>68.028</t>
+          <t>7017.241</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>52.935</t>
+          <t>2.5441</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>38.169</t>
+          <t>68.003</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>14.766</t>
+          <t>6769.623</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>61.7052880644603</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>-1.094</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>15.1564782370786</t>
+          <t>-1.005</t>
         </is>
       </c>
     </row>
@@ -1055,74 +991,67 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>377958.374</t>
+          <t>377601.308</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>111798.111</t>
+          <t>33256.916</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>33117.1755</t>
+          <t>112049.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>57521.603</t>
+          <t>57499.844</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>56029.3395</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>56020.298</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>29.674</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7119.94</t>
+          <t>15.228</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.582</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>68.033</t>
+          <t>7114.472</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>53.456</t>
+          <t>2.5784</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>38.51</t>
+          <t>68.1591</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>14.946</t>
+          <t>6867.129</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>62.1130363760087</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>-0.578</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>15.2190312364927</t>
+          <t>0.515</t>
         </is>
       </c>
     </row>
@@ -1132,74 +1061,67 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>380877.269</t>
+          <t>380882.981</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>112702.352</t>
+          <t>33539.713</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>33369.232</t>
+          <t>113085.674</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>58401.6995</t>
+          <t>58455.257</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>55931.0855</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>55953.73</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>29.691</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7103.401</t>
+          <t>15.347</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.576</t>
+          <t>0.861</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>69.101</t>
+          <t>7087.171</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>53.994</t>
+          <t>2.5702</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>38.834</t>
+          <t>69.057</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>6851.839</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>62.5214020586588</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>-0.428</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>15.3334694016618</t>
+          <t>0.22</t>
         </is>
       </c>
     </row>
@@ -1209,74 +1131,67 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>383924.0725</t>
+          <t>384105.575</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>113741.622</t>
+          <t>33770.833</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>33606.2365</t>
+          <t>114172.774</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>59207.124</t>
+          <t>59304.834</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>56072.702</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>56164.631</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>29.722</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7171.594</t>
+          <t>15.44</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>0.824</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>69.197</t>
+          <t>7176.119</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>54.465</t>
+          <t>2.5995</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>39.067</t>
+          <t>69.2846</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>15.398</t>
+          <t>6946.143</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>62.9329042899607</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>-0.344</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>15.4215711493319</t>
+          <t>-0.207</t>
         </is>
       </c>
     </row>
@@ -1286,74 +1201,67 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>386932.4745</t>
+          <t>387244.118</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>115048.804</t>
+          <t>33946.173</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>33808.0165</t>
+          <t>115457.998</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>59911.5635</t>
+          <t>60050.103</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>56052.7335</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>56210.127</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>29.814</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7169.717</t>
+          <t>15.507</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.601</t>
+          <t>0.803</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>69.558</t>
+          <t>7167.868</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>55.013</t>
+          <t>2.5961</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>39.37</t>
+          <t>69.5294</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>15.643</t>
+          <t>6949.558</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>63.3517698046456</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>-0.473</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>15.4837258303064</t>
+          <t>-0.123</t>
         </is>
       </c>
     </row>
@@ -1363,74 +1271,67 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>390053.8575</t>
+          <t>390425.439</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>116340.44</t>
+          <t>34115.488</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>34025.0755</t>
+          <t>116657.804</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>60672.054</t>
+          <t>60812.196</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>56289.5315</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>56383.735</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>29.88</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7231.777</t>
+          <t>15.576</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.625</t>
+          <t>0.833</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>69.916</t>
+          <t>7258.911</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>55.455</t>
+          <t>2.6282</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>39.545</t>
+          <t>69.9197</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>15.909</t>
+          <t>7045.78</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>63.7797864105376</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>0.111</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>15.5547888665606</t>
+          <t>-0.114</t>
         </is>
       </c>
     </row>
@@ -1440,74 +1341,67 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>393287.6465</t>
+          <t>393751.009</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>117553.8855</t>
+          <t>34338.804</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>34293.091</t>
+          <t>117798.519</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>61597.542</t>
+          <t>61746.398</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>57083.8215</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>57122.325</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>29.915</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7238.713</t>
+          <t>15.682</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.627</t>
+          <t>0.863</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>69.784</t>
+          <t>7238.517</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>55.596</t>
+          <t>2.6233</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>69.8237</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>16.146</t>
+          <t>7034.877</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>64.1917604256299</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0.298</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>15.6622112461902</t>
+          <t>0.79</t>
         </is>
       </c>
     </row>
@@ -1517,74 +1411,67 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>396502.2875</t>
+          <t>397128.922</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>118944.53</t>
+          <t>34649.756</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>34605.406</t>
+          <t>119222.442</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>62478.109</t>
+          <t>62647.089</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>57999.66</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>58112.352</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>30.022</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7354.56</t>
+          <t>15.775</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.669</t>
+          <t>0.845</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>69.954</t>
+          <t>7371.409</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>55.651</t>
+          <t>2.6682</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>39.302</t>
+          <t>69.9476</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>16.349</t>
+          <t>7171.223</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>64.6444969543046</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0.314</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>15.7573136321439</t>
+          <t>0.496</t>
         </is>
       </c>
     </row>
@@ -1594,74 +1481,67 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>399858.8165</t>
+          <t>400494.308</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>120193.3745</t>
+          <t>35051.607</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>34996.7995</t>
+          <t>120527.504</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>63234.7365</t>
+          <t>63406.888</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>58762.644</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>58929.02</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>30.095</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7446.114</t>
+          <t>15.832</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>0.842</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>70.623</t>
+          <t>7459.573</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>55.849</t>
+          <t>2.697</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>39.244</t>
+          <t>70.6321</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>16.604</t>
+          <t>7268.805</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>65.0963381731031</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0.219</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>15.8142659085272</t>
+          <t>-0.071</t>
         </is>
       </c>
     </row>
@@ -1671,74 +1551,67 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>403165.982</t>
+          <t>403809.368</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>120903.6295</t>
+          <t>35372.16</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>35326.4295</t>
+          <t>121192.849</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>64146.912</t>
+          <t>64314.266</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>59379.1015</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>59506.281</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>30.013</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7300.879</t>
+          <t>15.927</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.642</t>
+          <t>0.806</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>70.666</t>
+          <t>7318.28</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>56.184</t>
+          <t>2.6422</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>39.249</t>
+          <t>70.6642</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>16.935</t>
+          <t>7141.39</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>65.5446022657292</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>0.157</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>15.9107947753389</t>
+          <t>0.33</t>
         </is>
       </c>
     </row>
@@ -1748,74 +1621,67 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>406302.0965</t>
+          <t>406994.972</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>121348.931</t>
+          <t>35541.916</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>35482.497</t>
+          <t>121671.32</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>64871.645</t>
+          <t>65090.578</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60081.5365</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>60283.315</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>29.895</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7213.942</t>
+          <t>15.993</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.599</t>
+          <t>0.765</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>70.913</t>
+          <t>7234.18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>56.554</t>
+          <t>2.6063</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>39.26</t>
+          <t>70.9094</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>17.293</t>
+          <t>7063.438</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>65.9900507154908</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>0.262</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>15.9663574367011</t>
+          <t>0.194</t>
         </is>
       </c>
     </row>
@@ -1825,74 +1691,67 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>409355.0465</t>
+          <t>409809.406</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>121747.859</t>
+          <t>35534.921</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>35475.085</t>
+          <t>122032.257</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>65143.9635</t>
+          <t>65337.382</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61021.297</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>61215.786</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>29.779</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7090.074</t>
+          <t>15.944</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.538</t>
+          <t>0.613</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>71.091</t>
+          <t>7119.876</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>56.918</t>
+          <t>2.5385</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>39.256</t>
+          <t>71.1157</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>17.662</t>
+          <t>6959.369</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>66.4361189945105</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>0.334</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>15.9138049126261</t>
+          <t>-0.945</t>
         </is>
       </c>
     </row>
@@ -1902,74 +1761,67 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>412150.778</t>
+          <t>412414.812</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>122079.0895</t>
+          <t>35315.708</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>35256.177</t>
+          <t>122318.038</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>65302.072</t>
+          <t>65467.579</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61954.5305</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>62136.601</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>29.661</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6969.117</t>
+          <t>15.876</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.473</t>
+          <t>0.654</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>70.964</t>
+          <t>6958.955</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>57.199</t>
+          <t>2.4719</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>39.199</t>
+          <t>70.9472</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6805.484</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>66.8503195547098</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>0.118</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>15.8442190299589</t>
+          <t>0.365</t>
         </is>
       </c>
     </row>
@@ -1979,74 +1831,67 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>414640.9005</t>
+          <t>415137.363</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>122322.554</t>
+          <t>34858.491</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>34795.566</t>
+          <t>122578.976</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>65549.785</t>
+          <t>65743.02</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>62782.9565</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>63059.243</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>29.527</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6870.203</t>
+          <t>15.836</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.415</t>
+          <t>0.662</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>70.809</t>
+          <t>6887.523</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>57.399</t>
+          <t>2.4148</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>39.093</t>
+          <t>70.8195</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>18.307</t>
+          <t>6738.015</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>67.2041937246783</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>0.064</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>15.8088082774651</t>
+          <t>0.875</t>
         </is>
       </c>
     </row>
@@ -2056,74 +1901,67 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>416909.4875</t>
+          <t>417428.148</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>122437.8395</t>
+          <t>34220.222</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>34184.1175</t>
+          <t>122607.258</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>65930.782</t>
+          <t>66099.319</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>63772.5335</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>64010.986</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>29.371</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6743.355</t>
+          <t>15.835</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.346</t>
+          <t>0.439</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>71.212</t>
+          <t>6738.051</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>57.545</t>
+          <t>2.3427</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>38.913</t>
+          <t>71.2184</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>18.632</t>
+          <t>6595.708</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>67.5569336220464</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>-0.339</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>15.8141716551844</t>
+          <t>-1.118</t>
         </is>
       </c>
     </row>
@@ -2133,74 +1971,67 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>419295.613</t>
+          <t>419814.08</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>122515.672</t>
+          <t>33686.912</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>33655.05</t>
+          <t>122709.848</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>66406.465</t>
+          <t>66622.925</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>64609.909</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>64904.054</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>29.23</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6754.745</t>
+          <t>15.868</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.325</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>71.354</t>
+          <t>6729.816</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>57.641</t>
+          <t>2.3173</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>38.684</t>
+          <t>71.3894</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>18.957</t>
+          <t>6592.336</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>67.9073400657988</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>0.811</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>15.8376245639374</t>
+          <t>1.598</t>
         </is>
       </c>
     </row>
@@ -2210,74 +2041,67 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>421868.879</t>
+          <t>422645.666</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>122584.747</t>
+          <t>33272.24</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>33233.292</t>
+          <t>122832.409</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>66947.109</t>
+          <t>67205.063</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>65026.3815</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>65400.626</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>29.061</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6555.708</t>
+          <t>15.901</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.229</t>
+          <t>0.645</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>71.692</t>
+          <t>6544.719</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>57.679</t>
+          <t>2.2225</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>38.411</t>
+          <t>71.6711</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>19.268</t>
+          <t>6420.112</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>68.2471086547701</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>1.035</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>15.8691746019975</t>
+          <t>1.514</t>
         </is>
       </c>
     </row>
@@ -2287,74 +2111,67 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>424262.833</t>
+          <t>425237.661</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>122436.5245</t>
+          <t>32786.167</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>32755.8015</t>
+          <t>122708.226</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>67555.618</t>
+          <t>67833.686</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>65293.0005</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>65733.303</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>28.855</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6369.601</t>
+          <t>15.952</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2.137</t>
+          <t>0.578</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>71.792</t>
+          <t>6380.637</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>57.626</t>
+          <t>2.1366</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>38.058</t>
+          <t>71.813</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>19.568</t>
+          <t>6261.904</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>68.5703779107393</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>0.968</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>15.9230582425305</t>
+          <t>1.399</t>
         </is>
       </c>
     </row>
@@ -2364,74 +2181,67 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>426507.1465</t>
+          <t>427470.508</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>122128.14</t>
+          <t>32284.512</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>32276.0705</t>
+          <t>122394.083</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>68264.9885</t>
+          <t>68548.617</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>65612.5685</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>66071.277</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>28.632</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6329.678</t>
+          <t>16.036</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2.098</t>
+          <t>0.469</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>72.083</t>
+          <t>6341.87</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>57.505</t>
+          <t>2.0958</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>37.649</t>
+          <t>72.0612</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>19.855</t>
+          <t>6228.062</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>68.8927533308014</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>0.971</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>16.0055907761912</t>
+          <t>0.404</t>
         </is>
       </c>
     </row>
@@ -2441,74 +2251,67 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>428512.642</t>
+          <t>429229.461</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>121649.367</t>
+          <t>31778.962</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>31795.457</t>
+          <t>121888.832</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>68902.025</t>
+          <t>69158.053</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>66012.3295</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>66410.557</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>28.396</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6174.114</t>
+          <t>16.112</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.021</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>72.106</t>
+          <t>6183.315</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>57.307</t>
+          <t>2.0195</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>37.18</t>
+          <t>72.1304</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>20.127</t>
+          <t>6078.191</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>69.1959541666985</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>0.471</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>16.0793447489467</t>
+          <t>-0.193</t>
         </is>
       </c>
     </row>
@@ -2518,74 +2321,67 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>430249.785</t>
+          <t>430806.922</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>120992.972</t>
+          <t>31199.381</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>31229.0015</t>
+          <t>121216.693</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>69373.657</t>
+          <t>69611.926</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>66471.866</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>66819.385</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>28.136</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6101.5</t>
+          <t>16.157</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.976</t>
+          <t>0.382</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>72.317</t>
+          <t>6109.4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>56.999</t>
+          <t>1.9763</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>36.646</t>
+          <t>72.3239</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>20.353</t>
+          <t>6011.328</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>69.468569689095</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>0.493</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>16.124042223519</t>
+          <t>0.329</t>
         </is>
       </c>
     </row>
@@ -2595,74 +2391,67 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>431967.585</t>
+          <t>432496.627</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>120220.687</t>
+          <t>30625.185</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>30650.861</t>
+          <t>120433.545</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>69700.032</t>
+          <t>69948.936</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>67005.0915</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>67327.049</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>27.847</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6015.382</t>
+          <t>16.175</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.929</t>
+          <t>0.401</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>72.762</t>
+          <t>6025.373</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>56.652</t>
+          <t>1.9304</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>36.071</t>
+          <t>72.7739</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>20.582</t>
+          <t>5935.285</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>69.7405720650475</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>0.532</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>16.1354773877304</t>
+          <t>0.491</t>
         </is>
       </c>
     </row>
@@ -2672,74 +2461,67 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>433614.523</t>
+          <t>434206.53</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>119308.7605</t>
+          <t>30165.193</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>30178.637</t>
+          <t>119529.216</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>69871.6565</t>
+          <t>70155.41</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>67613.5705</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>67934.796</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>27.525</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5967.313</t>
+          <t>16.156</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.897</t>
+          <t>0.388</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>72.822</t>
+          <t>5975.5</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>56.241</t>
+          <t>1.8965</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>35.432</t>
+          <t>72.8458</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>20.808</t>
+          <t>5890.588</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>70.0145461561994</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>0.418</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>16.1137722086859</t>
+          <t>0.66</t>
         </is>
       </c>
     </row>
@@ -2749,74 +2531,67 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>435202.746</t>
+          <t>436003.138</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>118311.9035</t>
+          <t>29818.156</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>29812.578</t>
+          <t>118584.788</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>69901.0495</t>
+          <t>70234.638</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>68317.886</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>68690.187</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>27.198</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5974.54</t>
+          <t>16.11</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.882</t>
+          <t>0.438</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>73.121</t>
+          <t>5985.438</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>55.702</t>
+          <t>1.8827</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>34.727</t>
+          <t>73.1019</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>20.975</t>
+          <t>5905.027</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>70.2750596983435</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>0.485</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>16.0617206905216</t>
+          <t>1.128</t>
         </is>
       </c>
     </row>
@@ -2826,74 +2601,67 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>436910.7285</t>
+          <t>438054.779</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>117329.405</t>
+          <t>29631.342</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>29573.0235</t>
+          <t>117748.839</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>69802.999</t>
+          <t>70194.385</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69011.905</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>69467.889</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>26.878</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>5975.404</t>
+          <t>16.024</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.867</t>
+          <t>0.501</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>73.192</t>
+          <t>6007.914</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>54.946</t>
+          <t>1.8723</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>33.993</t>
+          <t>73.2468</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>20.953</t>
+          <t>5931.44</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>70.5205883398261</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>1.056</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>15.9764900348517</t>
+          <t>1.832</t>
         </is>
       </c>
     </row>
@@ -2903,74 +2671,67 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>438522.5615</t>
+          <t>439883.304</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>116193.718</t>
+          <t>29506.219</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>29399.9625</t>
+          <t>116704.113</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>69570.086</t>
+          <t>69993.959</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69567.949</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>70085.874</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>26.532</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5857.5</t>
+          <t>15.912</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.813</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>73.52</t>
+          <t>5887.301</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>53.908</t>
+          <t>1.8163</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>33.224</t>
+          <t>73.4986</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>20.683</t>
+          <t>5816.425</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>70.7364945178425</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>0.421</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>15.864653750546</t>
+          <t>0.442</t>
         </is>
       </c>
     </row>
@@ -2980,74 +2741,67 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>439902.19</t>
+          <t>441199.648</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>114798.609</t>
+          <t>29348.171</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>29246.8725</t>
+          <t>115258.136</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>69145.0515</t>
+          <t>69547.392</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69897.806</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>70416.159</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>26.125</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5813.574</t>
+          <t>15.763</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.785</t>
+          <t>0.265</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>73.817</t>
+          <t>5849.626</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>52.764</t>
+          <t>1.7893</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>32.458</t>
+          <t>73.8166</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>20.307</t>
+          <t>5781.982</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>70.8663801023319</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>0.222</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>15.7182785336895</t>
+          <t>-0.227</t>
         </is>
       </c>
     </row>
@@ -3057,74 +2811,67 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>441154.3725</t>
+          <t>442316.394</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>113340.261</t>
+          <t>29164.726</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>29082.7425</t>
+          <t>113705.402</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>68442.631</t>
+          <t>68785.551</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>70044.5485</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>70532.174</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>25.706</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5693.663</t>
+          <t>15.552</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.734</t>
+          <t>0.241</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>73.84</t>
+          <t>5711.471</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>51.636</t>
+          <t>1.7337</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>31.733</t>
+          <t>73.8463</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>19.903</t>
+          <t>5648.448</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>70.9648551318828</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>0.356</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>15.5144401294584</t>
+          <t>0.066</t>
         </is>
       </c>
     </row>
@@ -3134,74 +2881,67 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>442378.2025</t>
+          <t>443390.407</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>111910.806</t>
+          <t>28888.218</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>28823.735</t>
+          <t>112155.906</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>67516.718</t>
+          <t>67775.213</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>70068.3</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>70489.998</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>25.299</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5641.672</t>
+          <t>15.286</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.705</t>
+          <t>0.245</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>74.212</t>
+          <t>5654.448</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>50.731</t>
+          <t>1.7036</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>31.074</t>
+          <t>74.2246</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>19.657</t>
+          <t>5595.231</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>71.0368626215482</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>0.523</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>15.2622162707034</t>
+          <t>0.057</t>
         </is>
       </c>
     </row>
@@ -3211,74 +2951,67 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>443621.7565</t>
+          <t>444542.416</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>110564.3105</t>
+          <t>28530.01</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>28501.6005</t>
+          <t>110735.689</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>66540.644</t>
+          <t>66713.683</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69957.7365</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>70303.907</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>24.91</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5608.34</t>
+          <t>15.006</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.684</t>
+          <t>0.274</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>74.237</t>
+          <t>5614.634</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>50.28</t>
+          <t>1.6801</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>30.535</t>
+          <t>74.2708</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>19.745</t>
+          <t>5558.628</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>71.098177829838</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>0.704</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>14.9994095251278</t>
+          <t>0.685</t>
         </is>
       </c>
     </row>
@@ -3288,74 +3021,67 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>444878.1335</t>
+          <t>445804.986</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>109324.8865</t>
+          <t>28203.68</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>28195.0655</t>
+          <t>109464.669</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>65554.056</t>
+          <t>65671.219</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69736.9225</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>70034.594</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>24.554</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>5573.343</t>
+          <t>14.73</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.663</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>74.516</t>
+          <t>5585.993</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>50.072</t>
+          <t>1.6606</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>30.062</t>
+          <t>74.5306</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>5532.354</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>71.1855895113556</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>14.7352839044404</t>
+          <t>0.868</t>
         </is>
       </c>
     </row>
@@ -3365,74 +3091,67 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>446241.4085</t>
+          <t>447102.097</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>108154.008</t>
+          <t>27933.183</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>27935.99</t>
+          <t>108208.498</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>64572.41</t>
+          <t>64637.277</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69392.3245</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>69601.447</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>24.202</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>5556.119</t>
+          <t>14.457</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1.649</t>
+          <t>0.288</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>74.871</t>
+          <t>5564.61</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>49.894</t>
+          <t>1.6455</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>29.613</t>
+          <t>74.8999</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>20.281</t>
+          <t>5513.413</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>71.3296956576081</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>1.006</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>14.4702864346575</t>
+          <t>0.668</t>
         </is>
       </c>
     </row>
@@ -3442,74 +3161,67 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>447676.3405</t>
+          <t>448559.061</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>107074.6615</t>
+          <t>27711.234</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>27732.4425</t>
+          <t>107159.879</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>63693.7295</t>
+          <t>63775.801</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>68789.394</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>68869.082</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>23.888</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>5587.653</t>
+          <t>14.217</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.652</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>75.067</t>
+          <t>5603.734</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>49.784</t>
+          <t>1.6522</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>29.232</t>
+          <t>75.0677</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>20.552</t>
+          <t>5554.723</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>71.4669162574071</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>0.998</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>14.2276291458382</t>
+          <t>1.375</t>
         </is>
       </c>
     </row>
@@ -3519,74 +3231,67 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>449124.0425</t>
+          <t>450280.246</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>106021.1045</t>
+          <t>27597.325</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>27591.628</t>
+          <t>106275.795</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>62910.38</t>
+          <t>63064.589</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>67954.92</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>68043.144</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>23.602</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>5520.143</t>
+          <t>14.006</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1.627</t>
+          <t>0.404</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>75.188</t>
+          <t>5538.204</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>49.691</t>
+          <t>1.626</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>28.889</t>
+          <t>75.1993</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>20.802</t>
+          <t>5492.187</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>71.5522439272667</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>1.242</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>14.0073507643493</t>
+          <t>2.024</t>
         </is>
       </c>
     </row>
@@ -3596,74 +3301,67 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>450612.051</t>
+          <t>452113.864</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>105021.333</t>
+          <t>27543.373</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>27494.1445</t>
+          <t>105402.273</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>62195.8055</t>
+          <t>62428.482</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>67065.879</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>67253</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>23.313</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5545.718</t>
+          <t>13.807</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1.631</t>
+          <t>0.409</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>75.245</t>
+          <t>5591.2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>49.623</t>
+          <t>1.6358</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>28.574</t>
+          <t>75.2481</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>21.049</t>
+          <t>5546.563</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>71.6500193757679</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>1.451</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>13.8025171235378</t>
+          <t>2.083</t>
         </is>
       </c>
     </row>
@@ -3673,74 +3371,67 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>452198.8625</t>
+          <t>453963.47</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>104067.966</t>
+          <t>27406.482</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>27339.2805</t>
+          <t>104546.277</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>61494.4405</t>
+          <t>61808.676</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>66198.8925</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>66447.844</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>23.031</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>5464.086</t>
+          <t>13.616</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>0.407</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>75.357</t>
+          <t>5498.088</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>49.536</t>
+          <t>1.6051</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>28.243</t>
+          <t>75.3884</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>21.293</t>
+          <t>5455.581</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>71.7608029814801</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>1.941</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>13.5989816869564</t>
+          <t>2.293</t>
         </is>
       </c>
     </row>
@@ -3750,74 +3441,67 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>453827.579</t>
+          <t>455897.194</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>103215.06</t>
+          <t>27300.989</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>27179.396</t>
+          <t>103817.255</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>60807.745</t>
+          <t>61176.55</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>65314.066</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>65662.75</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>22.774</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>5365.747</t>
+          <t>13.419</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1.573</t>
+          <t>0.443</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>75.711</t>
+          <t>5399.924</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>49.469</t>
+          <t>1.5723</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>27.939</t>
+          <t>75.7113</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>5360.848</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>71.8737399765268</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>1.923</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>13.398865078669</t>
+          <t>2.758</t>
         </is>
       </c>
     </row>
@@ -3827,74 +3511,67 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>455306.01</t>
+          <t>457590.704</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>102485.2195</t>
+          <t>27219.117</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>27004.583</t>
+          <t>103191.708</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>60219.6445</t>
+          <t>60619.113</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>64429.798</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>64840.989</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>22.55</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>5207.054</t>
+          <t>13.246</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1.526</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>75.811</t>
+          <t>5248.074</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>49.469</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>27.688</t>
+          <t>75.8018</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>21.782</t>
+          <t>5213.222</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>71.9982759291022</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>1.887</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>13.2261914355139</t>
+          <t>1.847</t>
         </is>
       </c>
     </row>
@@ -3904,74 +3581,67 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>456599.9255</t>
+          <t>459091.747</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>101702.6125</t>
+          <t>26925.418</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>26670.7765</t>
+          <t>102444.028</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>59676.4685</t>
+          <t>60080.488</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>63615.6975</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>64004.968</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>22.314</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5075.304</t>
+          <t>13.086</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1.489</t>
+          <t>0.356</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.182</t>
+          <t>5114.375</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>49.433</t>
+          <t>1.4901</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>27.388</t>
+          <t>76.1698</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>22.045</t>
+          <t>5082.748</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>72.1374625076542</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>1.733</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>13.0697499423924</t>
+          <t>2.516</t>
         </is>
       </c>
     </row>
@@ -3981,74 +3651,67 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>457743.3515</t>
+          <t>460187.201</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>100868.0425</t>
+          <t>26447.515</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>26200.2635</t>
+          <t>101644.474</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>59186.8445</t>
+          <t>59619.758</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>62896.0715</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>63309.16</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>22.088</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4962.521</t>
+          <t>12.957</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1.459</t>
+          <t>0.121</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.31</t>
+          <t>5009.086</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>49.377</t>
+          <t>1.4629</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>27.044</t>
+          <t>76.3129</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>22.332</t>
+          <t>4980.439</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>72.2741440321405</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>1.664</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>12.9301374462454</t>
+          <t>0.551</t>
         </is>
       </c>
     </row>
@@ -4058,74 +3721,67 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>458779.5985</t>
+          <t>460960.288</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>100022.12</t>
+          <t>25935.521</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>25700.572</t>
+          <t>100841.356</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>58774.7295</t>
+          <t>59251.573</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>62208.693</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>62679.253</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>21.877</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4965.525</t>
+          <t>12.853</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>0.214</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.608</t>
+          <t>5013.568</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>49.304</t>
+          <t>1.4696</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>26.695</t>
+          <t>76.6102</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>22.609</t>
+          <t>4986.399</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>72.4084905225694</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>1.563</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>12.811103565234</t>
+          <t>1.381</t>
         </is>
       </c>
     </row>
@@ -4135,74 +3791,67 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>459809.941</t>
+          <t>461886.014</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>99160.777</t>
+          <t>25498.464</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>25264.5815</t>
+          <t>100031.549</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>58412.613</t>
+          <t>58921.272</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61558.533</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>62112.024</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>21.657</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4944.944</t>
+          <t>12.756</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>0.187</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.964</t>
+          <t>4992.18</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>49.206</t>
+          <t>1.4701</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>26.357</t>
+          <t>76.9678</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>22.849</t>
+          <t>4967.029</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>72.542027184236</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>1.519</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>12.703642916672</t>
+          <t>1.049</t>
         </is>
       </c>
     </row>
@@ -4212,74 +3861,67 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>460814.1455</t>
+          <t>462385.992</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>98231.567</t>
+          <t>25124.32</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>24907.3075</t>
+          <t>98951.748</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>58102.804</t>
+          <t>58466.513</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61021.5165</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>61476.197</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>21.402</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4904.63</t>
+          <t>12.646</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>77.157</t>
+          <t>4937.723</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>49.094</t>
+          <t>1.4614</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>26.032</t>
+          <t>77.1517</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>23.062</t>
+          <t>4913.869</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>72.6766596923706</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>1.511</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>12.6087283924317</t>
+          <t>-0.357</t>
         </is>
       </c>
     </row>
@@ -4289,74 +3931,67 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>461796.773</t>
+          <t>463091.2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>97290.3775</t>
+          <t>24883.546</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>24670.744</t>
+          <t>97888.417</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>57797.5825</t>
+          <t>58040.124</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>60538.0345</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>60832.487</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>21.141</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4884.316</t>
+          <t>12.534</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1.464</t>
+          <t>0.275</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>77.334</t>
+          <t>4893.837</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>49.013</t>
+          <t>1.4633</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>25.731</t>
+          <t>77.3556</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>23.283</t>
+          <t>4871.371</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>72.814444010078</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>1.638</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>12.5158047607232</t>
+          <t>2.214</t>
         </is>
       </c>
     </row>
@@ -4366,82 +4001,67 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>463032.85</t>
+          <t>464426.666</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>96426.7025</t>
+          <t>24778.881</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>24558.386</t>
+          <t>97086.608</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>57473.6995</t>
+          <t>57764.291</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60145.711</t>
+          <t>60459.133</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.331399333386066</t>
+          <t>20.905</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>4916.107</t>
+          <t>12.438</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>0.301</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.715</t>
+          <t>4937.573</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>48.986</t>
+          <t>1.4842</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>25.442</t>
+          <t>77.7083</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>23.544</t>
+          <t>4915.459</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>72.9546731236258</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>0.596531872053423</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>2.434</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>12.4124453588984</t>
+          <t>2.218</t>
         </is>
       </c>
     </row>
@@ -4451,74 +4071,67 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>464362.7675</t>
+          <t>465901.599</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>95606.5065</t>
+          <t>24687.654</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>24456.4325</t>
+          <t>96329</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>57140.041</t>
+          <t>57488.306</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>59830.136</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>60201.926</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>20.676</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4834.216</t>
+          <t>12.338</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>78.028</t>
+          <t>4856.122</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>48.983</t>
+          <t>1.4674</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>25.151</t>
+          <t>78.025</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>23.832</t>
+          <t>4835.25</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>73.1160415306224</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>1.868</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>12.305043599345</t>
+          <t>2.628</t>
         </is>
       </c>
     </row>
@@ -4528,74 +4141,67 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>465891.093</t>
+          <t>467758.688</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>94893.796</t>
+          <t>24605.609</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>24352.1865</t>
+          <t>95709.561</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>56796.5535</t>
+          <t>57221.274</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>59578.476</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>60000.947</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>20.46</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4804.984</t>
+          <t>12.233</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>0.462</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>78.189</t>
+          <t>4832.07</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>48.973</t>
+          <t>1.4671</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>24.866</t>
+          <t>78.1854</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>24.107</t>
+          <t>4812.176</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>73.34053596022</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>3.515</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>12.1909507078728</t>
+          <t>4.07</t>
         </is>
       </c>
     </row>
@@ -4605,74 +4211,67 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>467843.811</t>
+          <t>469929.8</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>94318.992</t>
+          <t>24567.284</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>24321.9005</t>
+          <t>95166.744</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>56444.8785</t>
+          <t>56905.165</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>59443.1825</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
+          <t>59870.691</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>20.249</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4841.849</t>
+          <t>12.108</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1.481</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>78.277</t>
+          <t>4872.055</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>48.929</t>
+          <t>1.4828</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>24.581</t>
+          <t>78.2809</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>24.349</t>
+          <t>4852.655</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>73.5593975314628</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>3.933</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>12.0648979793814</t>
+          <t>4.176</t>
         </is>
       </c>
     </row>
@@ -4682,74 +4281,67 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>470007.2145</t>
+          <t>472203.843</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>93816.5025</t>
+          <t>24590.141</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>24349.32</t>
+          <t>94634.557</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>56037.2405</t>
+          <t>56479.96</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>59309.2875</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>59754.28</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>20.041</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4911.58</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1.506</t>
+          <t>0.501</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t>4945.091</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>1.5078</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
           <t>78.87</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>48.931</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>24.306</t>
-        </is>
-      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>24.625</t>
+          <t>4925.971</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>73.7767422229295</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>3.913</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>11.9226341152259</t>
+          <t>3.981</t>
         </is>
       </c>
     </row>
@@ -4759,74 +4351,67 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>472199.0885</t>
+          <t>474456.174</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>93384.5735</t>
+          <t>24656.587</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>24396.8555</t>
+          <t>94185.552</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>55567.8595</t>
+          <t>55960.056</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>59118.4285</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+          <t>59626.527</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>19.851</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>4926.788</t>
+          <t>11.794</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>78.968</t>
+          <t>4958.557</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>49.009</t>
+          <t>1.5153</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>24.059</t>
+          <t>78.9724</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>24.951</t>
+          <t>4940.35</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>73.9949965156061</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>3.597</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>11.767887921283</t>
+          <t>3.628</t>
         </is>
       </c>
     </row>
@@ -4836,74 +4421,67 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>474373.821</t>
+          <t>476361.477</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>92990.472</t>
+          <t>24724.046</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>24510.5465</t>
+          <t>93731.869</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>55105.7405</t>
+          <t>55400.162</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>58920.7045</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+          <t>59330.382</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>19.676</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>5007.124</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1.545</t>
+          <t>0.351</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>79.325</t>
+          <t>5047.916</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>49.076</t>
+          <t>1.5449</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>23.838</t>
+          <t>79.3216</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>25.239</t>
+          <t>5029.777</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>74.2127345275637</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>3.646</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>11.616522257454</t>
+          <t>2.32</t>
         </is>
       </c>
     </row>
@@ -4913,74 +4491,67 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>476884.1735</t>
+          <t>478501.712</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>92695.6375</t>
+          <t>24899.515</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>24753.5865</t>
+          <t>93341.227</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54691.8065</t>
+          <t>54929.768</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>58749.668</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
+          <t>58985.376</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>19.508</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>5071.082</t>
+          <t>11.48</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1.569</t>
+          <t>0.545</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>79.465</t>
+          <t>5090.35</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>49.094</t>
+          <t>1.5694</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>23.656</t>
+          <t>79.4692</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>25.438</t>
+          <t>5072.535</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>74.4254453386724</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>4.648</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>11.468572357644</t>
+          <t>4.286</t>
         </is>
       </c>
     </row>
@@ -4990,74 +4561,67 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>479478.533</t>
+          <t>480914.987</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>92505.664</t>
+          <t>25211.411</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>25088.1335</t>
+          <t>93080.59</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>54236.07</t>
+          <t>54528.419</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>58523.6795</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
+          <t>58687.663</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>19.355</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>5201.28</t>
+          <t>11.338</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.462</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>79.662</t>
+          <t>5220.686</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>49.209</t>
+          <t>1.6116</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>23.556</t>
+          <t>79.6613</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>25.653</t>
+          <t>5202.984</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>74.6351903467866</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>3.758</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>11.3114699130858</t>
+          <t>3.287</t>
         </is>
       </c>
     </row>
@@ -5067,74 +4631,67 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>481663.224</t>
+          <t>482889.112</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>92320.615</t>
+          <t>25506.682</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>25401.91</t>
+          <t>92809.219</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>53718.084</t>
+          <t>54049.37</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>58131.8055</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+          <t>58298.907</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>19.22</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>5164.108</t>
+          <t>11.194</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1.602</t>
+          <t>0.358</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>79.888</t>
+          <t>5182.548</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>49.497</t>
+          <t>1.6043</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>23.543</t>
+          <t>79.9013</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>25.954</t>
+          <t>5165.327</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>74.8440676395822</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>2.811</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>11.1526231033159</t>
+          <t>2.354</t>
         </is>
       </c>
     </row>
@@ -5144,74 +4701,67 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>483558.998</t>
+          <t>484658.301</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>92159.52</t>
+          <t>25772.251</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>25644.0795</t>
+          <t>92639.939</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>53191.026</t>
+          <t>53517.932</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>57609.389</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>57859.019</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>19.117</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>5189.247</t>
+          <t>11.043</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
+          <t>0.373</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>5208.36</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t>1.616</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>80.176</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>49.795</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>23.557</t>
-        </is>
-      </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>26.237</t>
+          <t>5191.761</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>75.0513023887418</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>2.575</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>10.9999040902968</t>
+          <t>2.46</t>
         </is>
       </c>
     </row>
@@ -5221,74 +4771,67 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>485321.516</t>
+          <t>486374.309</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>92057.269</t>
+          <t>25937.226</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>25778.464</t>
+          <t>92580.19</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>52656.8615</t>
+          <t>52952.608</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>57072.8485</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>57344.976</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>19.034</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>5089.501</t>
+          <t>10.886</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>0.334</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>80.473</t>
+          <t>5096.247</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>50.223</t>
+          <t>1.5892</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>23.588</t>
+          <t>80.4685</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>26.635</t>
+          <t>5080.499</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>75.262055390295</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>2.347</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>10.8498922392717</t>
+          <t>2.258</t>
         </is>
       </c>
     </row>
@@ -5298,74 +4841,67 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>486845.1985</t>
+          <t>487745.428</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>92015.76</t>
+          <t>25875.433</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>25775.343</t>
+          <t>92474.988</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>52134.649</t>
+          <t>52363.085</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>56544.612</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>56705.073</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>18.961</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>5046.558</t>
+          <t>10.738</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1.587</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>80.525</t>
+          <t>5052.249</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>50.871</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>23.644</t>
+          <t>80.5351</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>27.227</t>
+          <t>5036.862</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>75.4649545949325</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>2.101</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>10.7086706740931</t>
+          <t>1.578</t>
         </is>
       </c>
     </row>
@@ -5375,74 +4911,67 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>488064.7255</t>
+          <t>488895.834</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>91981.685</t>
+          <t>25650.721</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>25606.111</t>
+          <t>92367.079</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>51705.811</t>
+          <t>51904.076</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>55942.825</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+          <t>56065.5</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>18.894</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>4922.331</t>
+          <t>10.616</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>0.242</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>80.756</t>
+          <t>4919.596</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>51.581</t>
+          <t>1.5558</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>23.709</t>
+          <t>80.7674</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>27.872</t>
+          <t>4905.031</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>75.6707583528121</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>1.707</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>10.5940479404714</t>
+          <t>1.973</t>
         </is>
       </c>
     </row>
@@ -5452,74 +4981,67 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>489231.7235</t>
+          <t>490256.01</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>91938.524</t>
+          <t>25406.939</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>25354.386</t>
+          <t>92343.36</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>51463.2695</t>
+          <t>51690.225</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>55323.3755</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+          <t>55525.092</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>18.833</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>4945.742</t>
+          <t>10.542</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1.573</t>
+          <t>0.314</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>81.115</t>
+          <t>4942.802</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>52.301</t>
+          <t>1.5725</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>23.771</t>
+          <t>81.0923</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>4928.37</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>75.8708126731612</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>1.954</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>10.5192012349134</t>
+          <t>2.553</t>
         </is>
       </c>
     </row>
@@ -5529,74 +5051,67 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>490441.161</t>
+          <t>492046.213</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>91937.37</t>
+          <t>25217.315</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>25134.16</t>
+          <t>92454.064</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>51385.2425</t>
+          <t>51709.73</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>54768.689</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+          <t>55099.034</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>18.79</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>4914.034</t>
+          <t>10.51</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1.573</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>80.879</t>
+          <t>4915.528</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>52.96</t>
+          <t>1.5719</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>23.825</t>
+          <t>80.8954</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>29.136</t>
+          <t>4901.236</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>76.0700392065835</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>2.305</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>10.4773511251027</t>
+          <t>4.123</t>
         </is>
       </c>
     </row>
@@ -5606,74 +5121,67 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>491694.204</t>
+          <t>493892.173</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>92001.0805</t>
+          <t>25100.075</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>24964.4635</t>
+          <t>92614.516</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>51422.8215</t>
+          <t>51876.275</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>54252.827</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+          <t>54794.022</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>18.753</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>4939.74</t>
+          <t>10.504</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>0.334</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>81.194</t>
+          <t>4957.467</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>53.589</t>
+          <t>1.5912</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>23.891</t>
+          <t>81.183</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>29.698</t>
+          <t>4942.962</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>76.2722736374914</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>2.506</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>10.4582931996489</t>
+          <t>3.096</t>
         </is>
       </c>
     </row>
@@ -5683,74 +5191,67 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>492993.99</t>
+          <t>495465.165</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>92082.421</t>
+          <t>24989.48</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>24838.939</t>
+          <t>92697.854</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>51560.2955</t>
+          <t>52048.031</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>53797.884</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+          <t>54433.506</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>18.707</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>4867.127</t>
+          <t>10.505</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1.577</t>
+          <t>0.302</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>81.198</t>
+          <t>4879.444</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>54.231</t>
+          <t>1.5744</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>23.979</t>
+          <t>81.2039</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>30.252</t>
+          <t>4865.299</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>76.4785415740317</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>2.685</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>10.4586052864458</t>
+          <t>3.188</t>
         </is>
       </c>
     </row>
@@ -5760,74 +5261,67 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>494256.1015</t>
+          <t>496976.105</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>92066.7125</t>
+          <t>24827.811</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>24700.5455</t>
+          <t>92661.624</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>51813.9015</t>
+          <t>52248.621</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>53470.1865</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
+          <t>54115.733</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>18.647</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>4764.596</t>
+          <t>10.513</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>0.307</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>81.339</t>
+          <t>4782.187</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>54.836</t>
+          <t>1.5485</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>24.038</t>
+          <t>81.2947</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>30.798</t>
+          <t>4768.57</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>76.6900449140039</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>2.952</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>10.4832092801185</t>
+          <t>3.513</t>
         </is>
       </c>
     </row>
@@ -5837,74 +5331,67 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>495570.3535</t>
+          <t>498490.97</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>91995.246</t>
+          <t>24621.857</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>24501.4595</t>
+          <t>92580.892</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>52123.39</t>
+          <t>52500.02</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>53299.615</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
+          <t>53953.597</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>18.572</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>4665.521</t>
+          <t>10.532</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>0.301</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>81.682</t>
+          <t>4696.094</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>55.415</t>
+          <t>1.5265</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>24.049</t>
+          <t>81.5654</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>31.366</t>
+          <t>4682.81</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>76.9075535931274</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>3.111</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>10.5178587927778</t>
+          <t>3.547</t>
         </is>
       </c>
     </row>
@@ -5914,82 +5401,67 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>496404.869</t>
+          <t>499425.284</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>91865.2495</t>
+          <t>24329.692</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>24184.9285</t>
+          <t>92437.239</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>52382.6215</t>
+          <t>52694.161</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>53203.9685</t>
+          <t>53822.139</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0.0498989682487103</t>
+          <t>18.507</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>4574.469</t>
+          <t>10.549</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>0.073</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>80.896</t>
+          <t>4588.429</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>55.926</t>
+          <t>1.4967</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>24.018</t>
+          <t>80.8229</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>31.908</t>
+          <t>4576.018</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>77.1303415010454</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>0.329643641470482</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>2.393</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>10.5523988121881</t>
+          <t>2.551</t>
         </is>
       </c>
     </row>
@@ -5999,74 +5471,67 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>496711.423</t>
+          <t>500003.476</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>91635.042</t>
+          <t>23941.886</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>23795.257</t>
+          <t>92170.48</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>52619.2145</t>
+          <t>52868.164</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>53158.902</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
+          <t>53745.153</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>18.436</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>4570.015</t>
+          <t>10.575</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.158</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>80.858</t>
+          <t>4621.075</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>56.366</t>
+          <t>1.5142</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>23.949</t>
+          <t>80.8368</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>32.417</t>
+          <t>4608.495</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>77.3604290282091</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>2.382</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>10.5935180999451</t>
+          <t>3.15</t>
         </is>
       </c>
     </row>
@@ -6076,74 +5541,67 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>499090.7275</t>
+          <t>502214.994</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>91608.558</t>
+          <t>23569.996</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>23515.632</t>
+          <t>92039.112</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>53109.3535</t>
+          <t>53257.528</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>53762.6375</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
+          <t>53900.934</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>18.325</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>4543.124</t>
+          <t>10.603</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>0.723</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>81.643</t>
+          <t>4415.167</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>56.585</t>
+          <t>1.4545</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>80.9793</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>32.815</t>
+          <t>4402.955</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>77.5230113014714</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>10.363</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>10.6412222415012</t>
+          <t>9.417</t>
         </is>
       </c>
     </row>
@@ -6153,416 +5611,2179 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>500906.348</t>
+          <t>504501.105</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>91342.9615</t>
+          <t>23170.962</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>23286.6345</t>
+          <t>91722.635</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>53334.661</t>
+          <t>53601.796</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>54135.9175</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
+          <t>54083.577</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>18.181</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>4618.262</t>
+          <t>10.625</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1.528</t>
+          <t>0.186</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>82.301</t>
+          <t>4306.217</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>56.911</t>
+          <t>1.419</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>23.566</t>
+          <t>81.8557</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>33.344</t>
+          <t>4294.976</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>77.7037053122399</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>-0.871</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>10.6476312813668</t>
+          <t>3.7</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="inlineStr">
+      <c r="A76" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>504836.177</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>22698.84</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>90943.363</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>53728.829</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>54368.045</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>18.014</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>10.643</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>-0.053</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>4281.794</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>1.4214</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>82.0128</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>4271.223</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>1.454</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>504256.74</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>22265.889</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>89923.211</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>53756.628</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>54818.63</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>17.833</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>10.662</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>-0.176</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>4240.165</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>1.4245</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>82.1707</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>4230.008</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>0.356</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>4179.562</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>4150.706</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>4129.062</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>4110.731</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>4098.079</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>4093.037</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>4096.183</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>2033</v>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>4105.122</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>2034</v>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>4123.985</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>2035</v>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>4145.787</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>2036</v>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>4173.018</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>2037</v>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>4198.503</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>4224.115</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>2039</v>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>4247.725</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>2040</v>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>4266.676</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>2041</v>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>4283.553</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>2042</v>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>4295.957</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>2043</v>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>4301.462</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>2044</v>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>4297.743</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>2045</v>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>4288.1</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>2046</v>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>4271.161</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>2047</v>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>4248.885</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>2048</v>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>4221.324</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>2049</v>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>4186.718</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>2050</v>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>4150.823</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>2051</v>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>4111.339</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>2052</v>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>4071.853</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>2053</v>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>4032.794</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>2054</v>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>3991.168</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>2055</v>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>3951.933</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>2056</v>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>3915.743</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>2057</v>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>3884.672</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>2058</v>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>3854.386</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>2059</v>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>3829.738</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>2060</v>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>3809.517</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>2061</v>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>3793.197</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>2062</v>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>3780.714</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>2063</v>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>3770.671</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>2064</v>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>3766.537</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>2065</v>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>3765.541</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>2066</v>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>3766.794</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>2067</v>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>3768.958</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>2068</v>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>3775.184</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>2069</v>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>3782.43</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>2070</v>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>3790.148</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>2071</v>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>3795.573</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>2072</v>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>3802.35</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>2073</v>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>3807.096</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>2074</v>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>3808.279</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>2075</v>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>3807.868</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>2076</v>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>3806.267</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>2077</v>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>3799.485</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>2078</v>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>3789.561</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>2079</v>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>3779.049</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>2080</v>
+      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>3764.904</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>2081</v>
+      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>3747.384</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>2082</v>
+      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>3728.789</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>2083</v>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>3708.846</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>2084</v>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>3688.121</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>2085</v>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>3666.852</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>2086</v>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>3644.986</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>2087</v>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>3624.616</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>2088</v>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>3604.006</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>2089</v>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>3583.79</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>2090</v>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>3565.37</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>2091</v>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>3549.013</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>2092</v>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>3532.696</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>2093</v>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>3519.435</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>2094</v>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>3507.694</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>2095</v>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>3497.137</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>2096</v>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>3487.894</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>2097</v>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>3480.901</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>2098</v>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>3476.566</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>2099</v>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>3472.634</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>2100</v>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>3469.579</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>Data Source</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>United Nations, Department of Economic and Social Affairs, Population Division (2024). World Population Prospects 2024.</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>United Nations, Department of Economic and Social Affairs, Population Division (2024). World Population Prospects 2024.</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>United Nations, Department of Economic and Social Affairs, Population Division (2024). World Population Prospects 2024.</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>United Nations, Department of Economic and Social Affairs, Population Division (2024). World Population Prospects 2024.</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>United Nations, Department of Economic and Social Affairs, Population Division (2024). World Population Prospects 2024.</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>United Nations, Department of Economic and Social Affairs, Population Division (2024). World Population Prospects 2024.</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>United Nations, Department of Economic and Social Affairs, Population Division (2024). World Population Prospects 2024.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>United Nations, Department of Economic and Social Affairs, Population Division (2024). World Population Prospects 2024.</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>United Nations, Department of Economic and Social Affairs, Population Division (2024). World Population Prospects 2024.</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>United Nations, Department of Economic and Social Affairs, Population Division (2024). World Population Prospects 2024.</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>United Nations, Department of Economic and Social Affairs, Population Division (2024). World Population Prospects 2024.</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>United Nations, Department of Economic and Social Affairs, Population Division (2024). World Population Prospects 2024.</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>United Nations, Department of Economic and Social Affairs, Population Division (2024). World Population Prospects 2024.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
         <is>
           <t>Unit of measure</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>Persons</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>Persons</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D154" t="inlineStr">
         <is>
           <t>Persons</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E154" t="inlineStr">
         <is>
           <t>Persons</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F154" t="inlineStr">
         <is>
           <t>Persons</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G154" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
         <is>
           <t>Persons</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="K154" t="inlineStr">
         <is>
           <t>Number</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="L154" t="inlineStr">
         <is>
           <t>Years</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Persons</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
         <is>
           <t>Number</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr">
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
         <is>
           <t>Unit multiplier</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>Thousands</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>Thousands</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D155" t="inlineStr">
         <is>
           <t>Thousands</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E155" t="inlineStr">
         <is>
           <t>Thousands</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>Thousands</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G155" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
         <is>
           <t>Thousands</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr">
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="inlineStr">
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Thousands</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
         <is>
           <t>Citation of or link to the data source</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>https://population.un.org/wpp/</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>https://population.un.org/wpp/</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D156" t="inlineStr">
         <is>
           <t>https://population.un.org/wpp/</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E156" t="inlineStr">
         <is>
           <t>https://population.un.org/wpp/</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>https://population.un.org/wpp/</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G156" t="inlineStr">
         <is>
           <t>https://population.un.org/wpp/</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H156" t="inlineStr">
         <is>
           <t>https://population.un.org/wpp/</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I156" t="inlineStr">
         <is>
           <t>https://population.un.org/wpp/</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="J156" t="inlineStr">
         <is>
           <t>https://population.un.org/wpp/</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="K156" t="inlineStr">
         <is>
           <t>https://population.un.org/wpp/</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="L156" t="inlineStr">
         <is>
           <t>https://population.un.org/wpp/</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="M156" t="inlineStr">
         <is>
           <t>https://population.un.org/wpp/</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>https://population.un.org/wup/</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>https://population.un.org/wup/</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
+      <c r="N156" t="inlineStr">
         <is>
           <t>https://population.un.org/wpp/</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>https://population.un.org/wpp/</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="inlineStr">
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
         <is>
           <t>Series footnote</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Data from 236 countries/areas with population more than 1K from WPP2022, countries/areas less than 1K population is not shown but calculated when aggregated.</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Data from 236 countries/areas with population more than 1K from WPP2022, countries/areas less than 1K population is not shown but calculated when aggregated.</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Data from 236 countries/areas with population more than 1K from WPP2022, countries/areas less than 1K population is not shown but calculated when aggregated.</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Data from 236 countries/areas with population more than 1K from WPP2022, countries/areas less than 1K population is not shown but calculated when aggregated.</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Data from 236 countries/areas with population more than 1K from WPP2022, countries/areas less than 1K population is not shown but calculated when aggregated.</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>based on ln(Pt/P0) / t (and then expressed in per cent), 236 countries/areas with population more than 1K from WPP2022, UNICEF aggregation calculated by total population from WPP2022</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Data from 237 countries/areas from WPP2022</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Data from 237 countries/areas from WPP2022</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Data from 237 countries/areas from WPP2022</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Data from 236 countries/areas with population more than 1K from WPP2022, countries/areas less than 1K population is not shown but calculated when aggregated.</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>Data from 236 countries/areas with population more than 1K from WPP2022, countries/areas less than 1K population is not shown but calculated when aggregated.</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>Data from 236 countries/areas with population more than 1K from WPP2022, countries/areas less than 1K population is not shown but calculated when aggregated.</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>233 countries from WUP2018, used WPP2019 total population data when calculating UNICEF aggregation</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>based on ln(Pt/P0) / t (and then expressed in per cent), population data from WPP2019 and urban population percentage from WUP2018</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Data from 237 countries/areas from WPP2022</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>Data from 236 countries/areas with population more than 1K from WPP2022, countries/areas less than 1K population is not shown but calculated when aggregated.</t>
-        </is>
-      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>Observation footnote</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
